--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D3">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H3">
         <v>426</v>
